--- a/API Cases/API Sheet.xlsx
+++ b/API Cases/API Sheet.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elwady\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elwady\Downloads\API Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BE678F6-98F6-491D-994C-1D061160C7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B2E7EFF-B540-4634-8B8B-1982C4613B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="1" activeTab="2" xr2:uid="{0449AC7C-FFA0-44DC-97D5-ED3A5A82DE03}"/>
   </bookViews>
   <sheets>
     <sheet name="API TestCases_ِAya-tallah" sheetId="1" r:id="rId1"/>
     <sheet name="Bug Report_Aya-tallah" sheetId="2" r:id="rId2"/>
-    <sheet name="API TestCases_Omnia" sheetId="3" r:id="rId3"/>
+    <sheet name="API Bug_Omnia" sheetId="4" r:id="rId3"/>
+    <sheet name="API TestCases_Omnia" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="4">
+  <futureMetadata name="XLRICHVALUE" count="6">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -71,8 +72,22 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="4">
+  <valueMetadata count="6">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -85,12 +100,18 @@
     <bk>
       <rc t="1" v="3"/>
     </bk>
+    <bk>
+      <rc t="1" v="4"/>
+    </bk>
+    <bk>
+      <rc t="1" v="5"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="95">
   <si>
     <t>TC_ID</t>
   </si>
@@ -473,6 +494,39 @@
   </si>
   <si>
     <t>OK</t>
+  </si>
+  <si>
+    <t>BUG-API-001</t>
+  </si>
+  <si>
+    <t>API returns HTTP Status '200 OK' instead of '405 Method Not Allowed' for unsupported requests</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>1. Open Postman.
+2. Set Method to POST.
+3. Enter URL: .../api/productsList.
+4. Click Send.</t>
+  </si>
+  <si>
+    <t>The API should return HTTP Status 405 Method Not Allowed because POST is not supported on this endpoint.</t>
+  </si>
+  <si>
+    <t>The API returns HTTP Status 200 OK (Success), even though the response body contains an error message: "This request method is not supported."</t>
+  </si>
+  <si>
+    <t>API_ID</t>
+  </si>
+  <si>
+    <t>API_02</t>
+  </si>
+  <si>
+    <t>API_04</t>
+  </si>
+  <si>
+    <t>BUG-API-002</t>
   </si>
 </sst>
 </file>
@@ -592,14 +646,14 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -666,7 +720,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -681,6 +735,14 @@
   </rv>
   <rv s="0">
     <v>3</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>4</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>5</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -701,6 +763,8 @@
   <rel r:id="rId2"/>
   <rel r:id="rId3"/>
   <rel r:id="rId4"/>
+  <rel r:id="rId5"/>
+  <rel r:id="rId6"/>
 </richValueRels>
 </file>
 
@@ -1081,10 +1145,10 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="90.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1116,8 +1180,8 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="82.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
       <c r="C3" s="1" t="s">
         <v>23</v>
       </c>
@@ -1144,8 +1208,8 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
@@ -1170,8 +1234,8 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
       <c r="C5" s="1" t="s">
         <v>25</v>
       </c>
@@ -1210,7 +1274,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D30BE5B5-4167-4C09-A600-4B5FE859C9DE}">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" customWidth="1"/>
@@ -1415,6 +1479,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" s="7" customFormat="1" ht="12.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1422,6 +1487,114 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BDC4040-8650-44CB-AACE-6E3EF09412EF}">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="3" max="3" width="46.5703125" customWidth="1"/>
+    <col min="4" max="4" width="36.28515625" customWidth="1"/>
+    <col min="5" max="5" width="37.140625" customWidth="1"/>
+    <col min="6" max="6" width="41" customWidth="1"/>
+    <col min="7" max="7" width="27.140625" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="5" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" s="2" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" s="2" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63BB8B94-5D4E-465F-A184-CE49192C50B4}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1439,7 +1612,7 @@
       <c r="A1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>63</v>
       </c>
       <c r="C1" s="5" t="s">
@@ -1474,7 +1647,7 @@
       <c r="E2" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>73</v>
       </c>
       <c r="G2" s="3" t="s">
@@ -1497,7 +1670,7 @@
       <c r="E3" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="10" t="s">
         <v>73</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -1520,7 +1693,7 @@
       <c r="E4" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>73</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -1543,7 +1716,7 @@
       <c r="E5" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="10" t="s">
         <v>73</v>
       </c>
       <c r="G5" s="1" t="s">
